--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -527,10 +527,10 @@
         <v>10920</v>
       </c>
       <c r="F3" t="n">
-        <v>9158</v>
+        <v>9157</v>
       </c>
       <c r="G3" t="n">
-        <v>100005360</v>
+        <v>99994440</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -559,10 +559,10 @@
         <v>22250</v>
       </c>
       <c r="F4" t="n">
-        <v>6742</v>
+        <v>6741</v>
       </c>
       <c r="G4" t="n">
-        <v>150009500</v>
+        <v>149987250</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -687,10 +687,10 @@
         <v>426000</v>
       </c>
       <c r="F8" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G8" t="n">
-        <v>100110000</v>
+        <v>99684000</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -719,10 +719,10 @@
         <v>105200</v>
       </c>
       <c r="F9" t="n">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G9" t="n">
-        <v>100045200</v>
+        <v>99940000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -751,10 +751,10 @@
         <v>2370</v>
       </c>
       <c r="F10" t="n">
-        <v>421941</v>
+        <v>421940</v>
       </c>
       <c r="G10" t="n">
-        <v>1000000170</v>
+        <v>999997800</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -783,10 +783,10 @@
         <v>54200</v>
       </c>
       <c r="F11" t="n">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="G11" t="n">
-        <v>150025600</v>
+        <v>149971400</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -815,10 +815,10 @@
         <v>8320</v>
       </c>
       <c r="F12" t="n">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="G12" t="n">
-        <v>50003200</v>
+        <v>49994880</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입(숏)</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>와이지-원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>019210</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,62 +492,64 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18020</v>
+        <v>14260</v>
       </c>
       <c r="F2" t="n">
-        <v>5549</v>
+        <v>3604</v>
       </c>
       <c r="G2" t="n">
-        <v>99992980</v>
+        <v>51393040</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10920</v>
+        <v>17160</v>
       </c>
       <c r="F3" t="n">
-        <v>9157</v>
+        <v>5549</v>
       </c>
       <c r="G3" t="n">
-        <v>99994440</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>95220840</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-4.77</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,30 +558,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22250</v>
+        <v>19630</v>
       </c>
       <c r="F4" t="n">
-        <v>6741</v>
+        <v>2618</v>
       </c>
       <c r="G4" t="n">
-        <v>149987250</v>
+        <v>51391340</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,126 +590,128 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23450</v>
+        <v>66600</v>
       </c>
       <c r="F5" t="n">
-        <v>4264</v>
+        <v>1543</v>
       </c>
       <c r="G5" t="n">
-        <v>99990800</v>
+        <v>102763800</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33600</v>
+        <v>11330</v>
       </c>
       <c r="F6" t="n">
-        <v>1488</v>
+        <v>9157</v>
       </c>
       <c r="G6" t="n">
-        <v>49996800</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>103748810</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>307500</v>
+        <v>21600</v>
       </c>
       <c r="F7" t="n">
-        <v>325</v>
+        <v>2776</v>
       </c>
       <c r="G7" t="n">
-        <v>99937500</v>
+        <v>59961600</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>426000</v>
+        <v>22200</v>
       </c>
       <c r="F8" t="n">
-        <v>234</v>
+        <v>366</v>
       </c>
       <c r="G8" t="n">
-        <v>99684000</v>
+        <v>8125200</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,111 +720,593 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105200</v>
+        <v>20650</v>
       </c>
       <c r="F9" t="n">
-        <v>950</v>
+        <v>2488</v>
       </c>
       <c r="G9" t="n">
-        <v>99940000</v>
+        <v>51377200</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2370</v>
+        <v>31900</v>
       </c>
       <c r="F10" t="n">
-        <v>421940</v>
+        <v>123</v>
       </c>
       <c r="G10" t="n">
-        <v>999997800</v>
+        <v>3923700</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>54200</v>
+        <v>288500</v>
       </c>
       <c r="F11" t="n">
-        <v>2767</v>
+        <v>147</v>
       </c>
       <c r="G11" t="n">
-        <v>149971400</v>
+        <v>42409500</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>386500</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>90441000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-9.27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101200</v>
+      </c>
+      <c r="F13" t="n">
+        <v>65</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6578000</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>114800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>895</v>
+      </c>
+      <c r="G14" t="n">
+        <v>102746000</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>626</v>
+      </c>
+      <c r="G15" t="n">
+        <v>30048000</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>파인엠텍</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>441270</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>9350</v>
+      </c>
+      <c r="F16" t="n">
+        <v>513</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4796550</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>동성화인텍</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>033500</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>18020</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5549</v>
+      </c>
+      <c r="G17" t="n">
+        <v>99992980</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>유니테스트</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>086390</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10920</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9157</v>
+      </c>
+      <c r="G18" t="n">
+        <v>99994440</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>086450</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>22250</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6741</v>
+      </c>
+      <c r="G19" t="n">
+        <v>149987250</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>23450</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4264</v>
+      </c>
+      <c r="G20" t="n">
+        <v>99990800</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>씨젠</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>096530</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>33600</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1488</v>
+      </c>
+      <c r="G21" t="n">
+        <v>49996800</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>307500</v>
+      </c>
+      <c r="F22" t="n">
+        <v>325</v>
+      </c>
+      <c r="G22" t="n">
+        <v>99937500</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>426000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>99684000</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>105200</v>
+      </c>
+      <c r="F24" t="n">
+        <v>950</v>
+      </c>
+      <c r="G24" t="n">
+        <v>99940000</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2370</v>
+      </c>
+      <c r="F25" t="n">
+        <v>421940</v>
+      </c>
+      <c r="G25" t="n">
+        <v>999997800</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2767</v>
+      </c>
+      <c r="G26" t="n">
+        <v>149971400</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>파인엠텍</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>441270</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
         <v>8320</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F27" t="n">
         <v>6009</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G27" t="n">
         <v>49994880</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,68 +488,68 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14260</v>
+        <v>13620</v>
       </c>
       <c r="F2" t="n">
         <v>3604</v>
       </c>
       <c r="G2" t="n">
-        <v>51393040</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>49086480</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-4.49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17160</v>
+        <v>25050</v>
       </c>
       <c r="F3" t="n">
-        <v>5549</v>
+        <v>3887</v>
       </c>
       <c r="G3" t="n">
-        <v>95220840</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-4.77</v>
-      </c>
+        <v>97369350</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,322 +558,320 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19630</v>
+        <v>194600</v>
       </c>
       <c r="F4" t="n">
-        <v>2618</v>
+        <v>250</v>
       </c>
       <c r="G4" t="n">
-        <v>51391340</v>
+        <v>48650000</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>66600</v>
+        <v>21200</v>
       </c>
       <c r="F5" t="n">
-        <v>1543</v>
+        <v>2618</v>
       </c>
       <c r="G5" t="n">
-        <v>102763800</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>55501600</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11330</v>
+        <v>68900</v>
       </c>
       <c r="F6" t="n">
-        <v>9157</v>
+        <v>271</v>
       </c>
       <c r="G6" t="n">
-        <v>103748810</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.75</v>
-      </c>
+        <v>18671900</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21600</v>
+        <v>91300</v>
       </c>
       <c r="F7" t="n">
-        <v>2776</v>
+        <v>213</v>
       </c>
       <c r="G7" t="n">
-        <v>59961600</v>
+        <v>19446900</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>22200</v>
+        <v>19930</v>
       </c>
       <c r="F8" t="n">
-        <v>366</v>
+        <v>7563</v>
       </c>
       <c r="G8" t="n">
-        <v>8125200</v>
+        <v>150730590</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20650</v>
+        <v>22500</v>
       </c>
       <c r="F9" t="n">
-        <v>2488</v>
+        <v>2034</v>
       </c>
       <c r="G9" t="n">
-        <v>51377200</v>
+        <v>45765000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>31900</v>
+        <v>20550</v>
       </c>
       <c r="F10" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G10" t="n">
-        <v>3923700</v>
+        <v>2445450</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>케이아이엔엑스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>093320</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>288500</v>
+        <v>139000</v>
       </c>
       <c r="F11" t="n">
-        <v>147</v>
+        <v>420</v>
       </c>
       <c r="G11" t="n">
-        <v>42409500</v>
+        <v>58380000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>386500</v>
+        <v>31450</v>
       </c>
       <c r="F12" t="n">
-        <v>234</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
-        <v>90441000</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-9.27</v>
-      </c>
+        <v>1981350</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101200</v>
+        <v>41300</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>1179</v>
       </c>
       <c r="G13" t="n">
-        <v>6578000</v>
+        <v>48692700</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -882,94 +880,94 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>114800</v>
+        <v>284000</v>
       </c>
       <c r="F14" t="n">
-        <v>895</v>
+        <v>240</v>
       </c>
       <c r="G14" t="n">
-        <v>102746000</v>
+        <v>68160000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>48000</v>
+        <v>21100</v>
       </c>
       <c r="F15" t="n">
-        <v>626</v>
+        <v>923</v>
       </c>
       <c r="G15" t="n">
-        <v>30048000</v>
+        <v>19475300</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9350</v>
+        <v>277000</v>
       </c>
       <c r="F16" t="n">
-        <v>513</v>
+        <v>103</v>
       </c>
       <c r="G16" t="n">
-        <v>4796550</v>
+        <v>28531000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -978,126 +976,126 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>18020</v>
+        <v>369000</v>
       </c>
       <c r="F17" t="n">
-        <v>5549</v>
+        <v>132</v>
       </c>
       <c r="G17" t="n">
-        <v>99992980</v>
+        <v>48708000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10920</v>
+        <v>91900</v>
       </c>
       <c r="F18" t="n">
-        <v>9157</v>
+        <v>485</v>
       </c>
       <c r="G18" t="n">
-        <v>99994440</v>
+        <v>44571500</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>22250</v>
+        <v>115800</v>
       </c>
       <c r="F19" t="n">
-        <v>6741</v>
+        <v>391</v>
       </c>
       <c r="G19" t="n">
-        <v>149987250</v>
+        <v>45277800</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>23450</v>
+        <v>46250</v>
       </c>
       <c r="F20" t="n">
-        <v>4264</v>
+        <v>1720</v>
       </c>
       <c r="G20" t="n">
-        <v>99990800</v>
+        <v>79550000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,62 +1104,64 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33600</v>
+        <v>34500</v>
       </c>
       <c r="F21" t="n">
-        <v>1488</v>
+        <v>847</v>
       </c>
       <c r="G21" t="n">
-        <v>49996800</v>
+        <v>29221500</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>307500</v>
+        <v>8070</v>
       </c>
       <c r="F22" t="n">
-        <v>325</v>
+        <v>5496</v>
       </c>
       <c r="G22" t="n">
-        <v>99937500</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>44352720</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>와이지-원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>019210</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,62 +1170,64 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>426000</v>
+        <v>14260</v>
       </c>
       <c r="F23" t="n">
-        <v>234</v>
+        <v>3604</v>
       </c>
       <c r="G23" t="n">
-        <v>99684000</v>
+        <v>51393040</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105200</v>
+        <v>17160</v>
       </c>
       <c r="F24" t="n">
-        <v>950</v>
+        <v>5549</v>
       </c>
       <c r="G24" t="n">
-        <v>99940000</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>95220840</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-4.77</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,30 +1236,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2370</v>
+        <v>19630</v>
       </c>
       <c r="F25" t="n">
-        <v>421940</v>
+        <v>2618</v>
       </c>
       <c r="G25" t="n">
-        <v>999997800</v>
+        <v>51391340</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,47 +1268,723 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>54200</v>
+        <v>66600</v>
       </c>
       <c r="F26" t="n">
-        <v>2767</v>
+        <v>1543</v>
       </c>
       <c r="G26" t="n">
-        <v>149971400</v>
+        <v>102763800</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>유니테스트</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>086390</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>11330</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9157</v>
+      </c>
+      <c r="G27" t="n">
+        <v>103748810</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>086450</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>21600</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2776</v>
+      </c>
+      <c r="G28" t="n">
+        <v>59961600</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F29" t="n">
+        <v>366</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8125200</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>091580</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20650</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2488</v>
+      </c>
+      <c r="G30" t="n">
+        <v>51377200</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>씨젠</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>096530</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>31900</v>
+      </c>
+      <c r="F31" t="n">
+        <v>123</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3923700</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>288500</v>
+      </c>
+      <c r="F32" t="n">
+        <v>147</v>
+      </c>
+      <c r="G32" t="n">
+        <v>42409500</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>386500</v>
+      </c>
+      <c r="F33" t="n">
+        <v>234</v>
+      </c>
+      <c r="G33" t="n">
+        <v>90441000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-9.27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101200</v>
+      </c>
+      <c r="F34" t="n">
+        <v>65</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6578000</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>114800</v>
+      </c>
+      <c r="F35" t="n">
+        <v>895</v>
+      </c>
+      <c r="G35" t="n">
+        <v>102746000</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F36" t="n">
+        <v>626</v>
+      </c>
+      <c r="G36" t="n">
+        <v>30048000</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>파인엠텍</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>441270</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>9350</v>
+      </c>
+      <c r="F37" t="n">
+        <v>513</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4796550</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>동성화인텍</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>033500</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>18020</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5549</v>
+      </c>
+      <c r="G38" t="n">
+        <v>99992980</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>유니테스트</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>086390</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>10920</v>
+      </c>
+      <c r="F39" t="n">
+        <v>9157</v>
+      </c>
+      <c r="G39" t="n">
+        <v>99994440</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>086450</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>22250</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6741</v>
+      </c>
+      <c r="G40" t="n">
+        <v>149987250</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>23450</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4264</v>
+      </c>
+      <c r="G41" t="n">
+        <v>99990800</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>씨젠</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>096530</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>33600</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1488</v>
+      </c>
+      <c r="G42" t="n">
+        <v>49996800</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>307500</v>
+      </c>
+      <c r="F43" t="n">
+        <v>325</v>
+      </c>
+      <c r="G43" t="n">
+        <v>99937500</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>426000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>234</v>
+      </c>
+      <c r="G44" t="n">
+        <v>99684000</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>105200</v>
+      </c>
+      <c r="F45" t="n">
+        <v>950</v>
+      </c>
+      <c r="G45" t="n">
+        <v>99940000</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2370</v>
+      </c>
+      <c r="F46" t="n">
+        <v>421940</v>
+      </c>
+      <c r="G46" t="n">
+        <v>999997800</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2767</v>
+      </c>
+      <c r="G47" t="n">
+        <v>149971400</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>파인엠텍</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>441270</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
         <v>8320</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F48" t="n">
         <v>6009</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G48" t="n">
         <v>49994880</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,27 +610,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>68900</v>
+        <v>21200</v>
       </c>
       <c r="F6" t="n">
-        <v>271</v>
+        <v>2296</v>
       </c>
       <c r="G6" t="n">
-        <v>18671900</v>
+        <v>48675200</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -642,27 +642,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>91300</v>
+        <v>68900</v>
       </c>
       <c r="F7" t="n">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="G7" t="n">
-        <v>19446900</v>
+        <v>18671900</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -674,27 +674,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19930</v>
+        <v>91300</v>
       </c>
       <c r="F8" t="n">
-        <v>7563</v>
+        <v>213</v>
       </c>
       <c r="G8" t="n">
-        <v>150730590</v>
+        <v>19446900</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22500</v>
+        <v>19930</v>
       </c>
       <c r="F9" t="n">
-        <v>2034</v>
+        <v>7563</v>
       </c>
       <c r="G9" t="n">
-        <v>45765000</v>
+        <v>150730590</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20550</v>
+        <v>22500</v>
       </c>
       <c r="F10" t="n">
-        <v>119</v>
+        <v>2034</v>
       </c>
       <c r="G10" t="n">
-        <v>2445450</v>
+        <v>45765000</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -770,27 +770,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>케이아이엔엑스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093320</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>139000</v>
+        <v>20550</v>
       </c>
       <c r="F11" t="n">
-        <v>420</v>
+        <v>119</v>
       </c>
       <c r="G11" t="n">
-        <v>58380000</v>
+        <v>2445450</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,27 +802,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>케이아이엔엑스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>093320</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31450</v>
+        <v>139000</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>420</v>
       </c>
       <c r="G12" t="n">
-        <v>1981350</v>
+        <v>58380000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,27 +834,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>41300</v>
+        <v>31450</v>
       </c>
       <c r="F13" t="n">
-        <v>1179</v>
+        <v>63</v>
       </c>
       <c r="G13" t="n">
-        <v>48692700</v>
+        <v>1981350</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>284000</v>
+        <v>41300</v>
       </c>
       <c r="F14" t="n">
-        <v>240</v>
+        <v>1179</v>
       </c>
       <c r="G14" t="n">
-        <v>68160000</v>
+        <v>48692700</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21100</v>
+        <v>284000</v>
       </c>
       <c r="F15" t="n">
-        <v>923</v>
+        <v>240</v>
       </c>
       <c r="G15" t="n">
-        <v>19475300</v>
+        <v>68160000</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,27 +930,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>277000</v>
+        <v>21100</v>
       </c>
       <c r="F16" t="n">
-        <v>103</v>
+        <v>923</v>
       </c>
       <c r="G16" t="n">
-        <v>28531000</v>
+        <v>19475300</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -962,27 +962,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>369000</v>
+        <v>277000</v>
       </c>
       <c r="F17" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="G17" t="n">
-        <v>48708000</v>
+        <v>28531000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,27 +994,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>91900</v>
+        <v>369000</v>
       </c>
       <c r="F18" t="n">
-        <v>485</v>
+        <v>132</v>
       </c>
       <c r="G18" t="n">
-        <v>44571500</v>
+        <v>48708000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115800</v>
+        <v>91900</v>
       </c>
       <c r="F19" t="n">
-        <v>391</v>
+        <v>485</v>
       </c>
       <c r="G19" t="n">
-        <v>45277800</v>
+        <v>44571500</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>46250</v>
+        <v>115800</v>
       </c>
       <c r="F20" t="n">
-        <v>1720</v>
+        <v>391</v>
       </c>
       <c r="G20" t="n">
-        <v>79550000</v>
+        <v>45277800</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1090,27 +1090,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>34500</v>
+        <v>46250</v>
       </c>
       <c r="F21" t="n">
-        <v>847</v>
+        <v>1720</v>
       </c>
       <c r="G21" t="n">
-        <v>29221500</v>
+        <v>79550000</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1122,63 +1122,63 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8070</v>
+        <v>34500</v>
       </c>
       <c r="F22" t="n">
-        <v>5496</v>
+        <v>847</v>
       </c>
       <c r="G22" t="n">
-        <v>44352720</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-3</v>
-      </c>
+        <v>29221500</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>와이지-원</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>019210</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>14260</v>
+        <v>8070</v>
       </c>
       <c r="F23" t="n">
-        <v>3604</v>
+        <v>5496</v>
       </c>
       <c r="G23" t="n">
-        <v>51393040</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>44352720</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1188,31 +1188,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>와이지-원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>019210</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>17160</v>
+        <v>14260</v>
       </c>
       <c r="F24" t="n">
-        <v>5549</v>
+        <v>3604</v>
       </c>
       <c r="G24" t="n">
-        <v>95220840</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-4.77</v>
-      </c>
+        <v>51393040</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1222,29 +1220,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>19630</v>
+        <v>17160</v>
       </c>
       <c r="F25" t="n">
-        <v>2618</v>
+        <v>5549</v>
       </c>
       <c r="G25" t="n">
-        <v>51391340</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>95220840</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-4.77</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1268,13 +1268,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>66600</v>
+        <v>19630</v>
       </c>
       <c r="F26" t="n">
-        <v>1543</v>
+        <v>2618</v>
       </c>
       <c r="G26" t="n">
-        <v>102763800</v>
+        <v>51391340</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1286,31 +1286,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>11330</v>
+        <v>66600</v>
       </c>
       <c r="F27" t="n">
-        <v>9157</v>
+        <v>1543</v>
       </c>
       <c r="G27" t="n">
-        <v>103748810</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3.75</v>
-      </c>
+        <v>102763800</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1320,29 +1318,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>21600</v>
+        <v>11330</v>
       </c>
       <c r="F28" t="n">
-        <v>2776</v>
+        <v>9157</v>
       </c>
       <c r="G28" t="n">
-        <v>59961600</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>103748810</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22200</v>
+        <v>21600</v>
       </c>
       <c r="F29" t="n">
-        <v>366</v>
+        <v>2776</v>
       </c>
       <c r="G29" t="n">
-        <v>8125200</v>
+        <v>59961600</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,27 +1384,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>20650</v>
+        <v>22200</v>
       </c>
       <c r="F30" t="n">
-        <v>2488</v>
+        <v>366</v>
       </c>
       <c r="G30" t="n">
-        <v>51377200</v>
+        <v>8125200</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>31900</v>
+        <v>20650</v>
       </c>
       <c r="F31" t="n">
-        <v>123</v>
+        <v>2488</v>
       </c>
       <c r="G31" t="n">
-        <v>3923700</v>
+        <v>51377200</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,27 +1448,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>288500</v>
+        <v>31900</v>
       </c>
       <c r="F32" t="n">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="G32" t="n">
-        <v>42409500</v>
+        <v>3923700</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,31 +1480,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>386500</v>
+        <v>288500</v>
       </c>
       <c r="F33" t="n">
-        <v>234</v>
+        <v>147</v>
       </c>
       <c r="G33" t="n">
-        <v>90441000</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-9.27</v>
-      </c>
+        <v>42409500</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1514,29 +1512,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101200</v>
+        <v>386500</v>
       </c>
       <c r="F34" t="n">
-        <v>65</v>
+        <v>234</v>
       </c>
       <c r="G34" t="n">
-        <v>6578000</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>90441000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-9.27</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1546,27 +1546,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>114800</v>
+        <v>101200</v>
       </c>
       <c r="F35" t="n">
-        <v>895</v>
+        <v>65</v>
       </c>
       <c r="G35" t="n">
-        <v>102746000</v>
+        <v>6578000</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1578,27 +1578,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>48000</v>
+        <v>114800</v>
       </c>
       <c r="F36" t="n">
-        <v>626</v>
+        <v>895</v>
       </c>
       <c r="G36" t="n">
-        <v>30048000</v>
+        <v>102746000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1624,45 +1624,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>9350</v>
+        <v>48000</v>
       </c>
       <c r="F37" t="n">
-        <v>513</v>
+        <v>626</v>
       </c>
       <c r="G37" t="n">
-        <v>4796550</v>
+        <v>30048000</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>18020</v>
+        <v>9350</v>
       </c>
       <c r="F38" t="n">
-        <v>5549</v>
+        <v>513</v>
       </c>
       <c r="G38" t="n">
-        <v>99992980</v>
+        <v>4796550</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10920</v>
+        <v>18020</v>
       </c>
       <c r="F39" t="n">
-        <v>9157</v>
+        <v>5549</v>
       </c>
       <c r="G39" t="n">
-        <v>99994440</v>
+        <v>99992980</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>22250</v>
+        <v>10920</v>
       </c>
       <c r="F40" t="n">
-        <v>6741</v>
+        <v>9157</v>
       </c>
       <c r="G40" t="n">
-        <v>149987250</v>
+        <v>99994440</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>23450</v>
+        <v>22250</v>
       </c>
       <c r="F41" t="n">
-        <v>4264</v>
+        <v>6741</v>
       </c>
       <c r="G41" t="n">
-        <v>99990800</v>
+        <v>149987250</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>33600</v>
+        <v>23450</v>
       </c>
       <c r="F42" t="n">
-        <v>1488</v>
+        <v>4264</v>
       </c>
       <c r="G42" t="n">
-        <v>49996800</v>
+        <v>99990800</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1816,13 +1816,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>307500</v>
+        <v>33600</v>
       </c>
       <c r="F43" t="n">
-        <v>325</v>
+        <v>1488</v>
       </c>
       <c r="G43" t="n">
-        <v>99937500</v>
+        <v>49996800</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>426000</v>
+        <v>307500</v>
       </c>
       <c r="F44" t="n">
-        <v>234</v>
+        <v>325</v>
       </c>
       <c r="G44" t="n">
-        <v>99684000</v>
+        <v>99937500</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105200</v>
+        <v>426000</v>
       </c>
       <c r="F45" t="n">
-        <v>950</v>
+        <v>234</v>
       </c>
       <c r="G45" t="n">
-        <v>99940000</v>
+        <v>99684000</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2370</v>
+        <v>105200</v>
       </c>
       <c r="F46" t="n">
-        <v>421940</v>
+        <v>950</v>
       </c>
       <c r="G46" t="n">
-        <v>999997800</v>
+        <v>99940000</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>54200</v>
+        <v>2370</v>
       </c>
       <c r="F47" t="n">
-        <v>2767</v>
+        <v>421940</v>
       </c>
       <c r="G47" t="n">
-        <v>149971400</v>
+        <v>999997800</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1962,29 +1962,61 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2767</v>
+      </c>
+      <c r="G48" t="n">
+        <v>149971400</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>파인엠텍</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>441270</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
         <v>8320</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F49" t="n">
         <v>6009</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G49" t="n">
         <v>49994880</v>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,21 +586,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>21200</v>
       </c>
       <c r="F5" t="n">
-        <v>2618</v>
+        <v>322</v>
       </c>
       <c r="G5" t="n">
-        <v>55501600</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8</v>
-      </c>
+        <v>6826400</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -610,27 +608,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21200</v>
+        <v>68900</v>
       </c>
       <c r="F6" t="n">
-        <v>2296</v>
+        <v>271</v>
       </c>
       <c r="G6" t="n">
-        <v>48675200</v>
+        <v>18671900</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -642,27 +640,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>68900</v>
+        <v>91300</v>
       </c>
       <c r="F7" t="n">
-        <v>271</v>
+        <v>213</v>
       </c>
       <c r="G7" t="n">
-        <v>18671900</v>
+        <v>19446900</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -674,27 +672,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>91300</v>
+        <v>19930</v>
       </c>
       <c r="F8" t="n">
-        <v>213</v>
+        <v>7563</v>
       </c>
       <c r="G8" t="n">
-        <v>19446900</v>
+        <v>150730590</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -706,12 +704,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -720,13 +718,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19930</v>
+        <v>22500</v>
       </c>
       <c r="F9" t="n">
-        <v>7563</v>
+        <v>2034</v>
       </c>
       <c r="G9" t="n">
-        <v>150730590</v>
+        <v>45765000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -738,12 +736,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,13 +750,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22500</v>
+        <v>20550</v>
       </c>
       <c r="F10" t="n">
-        <v>2034</v>
+        <v>119</v>
       </c>
       <c r="G10" t="n">
-        <v>45765000</v>
+        <v>2445450</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -770,27 +768,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>케이아이엔엑스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>093320</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20550</v>
+        <v>139000</v>
       </c>
       <c r="F11" t="n">
-        <v>119</v>
+        <v>420</v>
       </c>
       <c r="G11" t="n">
-        <v>2445450</v>
+        <v>58380000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,27 +800,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>케이아이엔엑스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093320</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>139000</v>
+        <v>31450</v>
       </c>
       <c r="F12" t="n">
-        <v>420</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
-        <v>58380000</v>
+        <v>1981350</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,27 +832,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>31450</v>
+        <v>41300</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>1179</v>
       </c>
       <c r="G13" t="n">
-        <v>1981350</v>
+        <v>48692700</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,12 +864,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +878,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>41300</v>
+        <v>284000</v>
       </c>
       <c r="F14" t="n">
-        <v>1179</v>
+        <v>240</v>
       </c>
       <c r="G14" t="n">
-        <v>48692700</v>
+        <v>68160000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,12 +896,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,13 +910,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>284000</v>
+        <v>21100</v>
       </c>
       <c r="F15" t="n">
-        <v>240</v>
+        <v>923</v>
       </c>
       <c r="G15" t="n">
-        <v>68160000</v>
+        <v>19475300</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,27 +928,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21100</v>
+        <v>277000</v>
       </c>
       <c r="F16" t="n">
-        <v>923</v>
+        <v>103</v>
       </c>
       <c r="G16" t="n">
-        <v>19475300</v>
+        <v>28531000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -962,27 +960,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>277000</v>
+        <v>369000</v>
       </c>
       <c r="F17" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="G17" t="n">
-        <v>28531000</v>
+        <v>48708000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,27 +992,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>369000</v>
+        <v>91900</v>
       </c>
       <c r="F18" t="n">
-        <v>132</v>
+        <v>485</v>
       </c>
       <c r="G18" t="n">
-        <v>48708000</v>
+        <v>44571500</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,12 +1024,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,13 +1038,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>91900</v>
+        <v>115800</v>
       </c>
       <c r="F19" t="n">
-        <v>485</v>
+        <v>391</v>
       </c>
       <c r="G19" t="n">
-        <v>44571500</v>
+        <v>45277800</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,12 +1056,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,13 +1070,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>115800</v>
+        <v>46250</v>
       </c>
       <c r="F20" t="n">
-        <v>391</v>
+        <v>1720</v>
       </c>
       <c r="G20" t="n">
-        <v>45277800</v>
+        <v>79550000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1090,27 +1088,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>46250</v>
+        <v>34500</v>
       </c>
       <c r="F21" t="n">
-        <v>1720</v>
+        <v>847</v>
       </c>
       <c r="G21" t="n">
-        <v>79550000</v>
+        <v>29221500</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1122,63 +1120,63 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>34500</v>
+        <v>8070</v>
       </c>
       <c r="F22" t="n">
-        <v>847</v>
+        <v>5496</v>
       </c>
       <c r="G22" t="n">
-        <v>29221500</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>44352720</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>와이지-원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>019210</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8070</v>
+        <v>14260</v>
       </c>
       <c r="F23" t="n">
-        <v>5496</v>
+        <v>3604</v>
       </c>
       <c r="G23" t="n">
-        <v>44352720</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-3</v>
-      </c>
+        <v>51393040</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1188,29 +1186,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>와이지-원</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>019210</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>14260</v>
+        <v>17160</v>
       </c>
       <c r="F24" t="n">
-        <v>3604</v>
+        <v>5549</v>
       </c>
       <c r="G24" t="n">
-        <v>51393040</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>95220840</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-4.77</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1220,31 +1220,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17160</v>
+        <v>19630</v>
       </c>
       <c r="F25" t="n">
-        <v>5549</v>
+        <v>2618</v>
       </c>
       <c r="G25" t="n">
-        <v>95220840</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-4.77</v>
-      </c>
+        <v>51391340</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1254,12 +1252,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1268,13 +1266,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>19630</v>
+        <v>66600</v>
       </c>
       <c r="F26" t="n">
-        <v>2618</v>
+        <v>1543</v>
       </c>
       <c r="G26" t="n">
-        <v>51391340</v>
+        <v>102763800</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1286,29 +1284,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>66600</v>
+        <v>11330</v>
       </c>
       <c r="F27" t="n">
-        <v>1543</v>
+        <v>9157</v>
       </c>
       <c r="G27" t="n">
-        <v>102763800</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>103748810</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1318,31 +1318,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>11330</v>
+        <v>21600</v>
       </c>
       <c r="F28" t="n">
-        <v>9157</v>
+        <v>2776</v>
       </c>
       <c r="G28" t="n">
-        <v>103748810</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3.75</v>
-      </c>
+        <v>59961600</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1352,12 +1350,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,13 +1364,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>21600</v>
+        <v>22200</v>
       </c>
       <c r="F29" t="n">
-        <v>2776</v>
+        <v>366</v>
       </c>
       <c r="G29" t="n">
-        <v>59961600</v>
+        <v>8125200</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,27 +1382,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>22200</v>
+        <v>20650</v>
       </c>
       <c r="F30" t="n">
-        <v>366</v>
+        <v>2488</v>
       </c>
       <c r="G30" t="n">
-        <v>8125200</v>
+        <v>51377200</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,27 +1414,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>20650</v>
+        <v>31900</v>
       </c>
       <c r="F31" t="n">
-        <v>2488</v>
+        <v>123</v>
       </c>
       <c r="G31" t="n">
-        <v>51377200</v>
+        <v>3923700</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,27 +1446,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>31900</v>
+        <v>288500</v>
       </c>
       <c r="F32" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="G32" t="n">
-        <v>3923700</v>
+        <v>42409500</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,29 +1478,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>288500</v>
+        <v>386500</v>
       </c>
       <c r="F33" t="n">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="G33" t="n">
-        <v>42409500</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>90441000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-9.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1512,31 +1512,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>386500</v>
+        <v>101200</v>
       </c>
       <c r="F34" t="n">
-        <v>234</v>
+        <v>65</v>
       </c>
       <c r="G34" t="n">
-        <v>90441000</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-9.27</v>
-      </c>
+        <v>6578000</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1546,27 +1544,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101200</v>
+        <v>114800</v>
       </c>
       <c r="F35" t="n">
-        <v>65</v>
+        <v>895</v>
       </c>
       <c r="G35" t="n">
-        <v>6578000</v>
+        <v>102746000</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1578,27 +1576,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>114800</v>
+        <v>48000</v>
       </c>
       <c r="F36" t="n">
-        <v>895</v>
+        <v>626</v>
       </c>
       <c r="G36" t="n">
-        <v>102746000</v>
+        <v>30048000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1610,12 +1608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1624,45 +1622,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48000</v>
+        <v>9350</v>
       </c>
       <c r="F37" t="n">
-        <v>626</v>
+        <v>513</v>
       </c>
       <c r="G37" t="n">
-        <v>30048000</v>
+        <v>4796550</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9350</v>
+        <v>18020</v>
       </c>
       <c r="F38" t="n">
-        <v>513</v>
+        <v>5549</v>
       </c>
       <c r="G38" t="n">
-        <v>4796550</v>
+        <v>99992980</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1674,12 +1672,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1688,13 +1686,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>18020</v>
+        <v>10920</v>
       </c>
       <c r="F39" t="n">
-        <v>5549</v>
+        <v>9157</v>
       </c>
       <c r="G39" t="n">
-        <v>99992980</v>
+        <v>99994440</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1706,12 +1704,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1720,13 +1718,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10920</v>
+        <v>22250</v>
       </c>
       <c r="F40" t="n">
-        <v>9157</v>
+        <v>6741</v>
       </c>
       <c r="G40" t="n">
-        <v>99994440</v>
+        <v>149987250</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1738,12 +1736,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1752,13 +1750,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>22250</v>
+        <v>23450</v>
       </c>
       <c r="F41" t="n">
-        <v>6741</v>
+        <v>4264</v>
       </c>
       <c r="G41" t="n">
-        <v>149987250</v>
+        <v>99990800</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1770,12 +1768,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1784,13 +1782,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23450</v>
+        <v>33600</v>
       </c>
       <c r="F42" t="n">
-        <v>4264</v>
+        <v>1488</v>
       </c>
       <c r="G42" t="n">
-        <v>99990800</v>
+        <v>49996800</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1802,12 +1800,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1816,13 +1814,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>33600</v>
+        <v>307500</v>
       </c>
       <c r="F43" t="n">
-        <v>1488</v>
+        <v>325</v>
       </c>
       <c r="G43" t="n">
-        <v>49996800</v>
+        <v>99937500</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1834,12 +1832,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1848,13 +1846,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>307500</v>
+        <v>426000</v>
       </c>
       <c r="F44" t="n">
-        <v>325</v>
+        <v>234</v>
       </c>
       <c r="G44" t="n">
-        <v>99937500</v>
+        <v>99684000</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1866,12 +1864,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1880,13 +1878,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>426000</v>
+        <v>105200</v>
       </c>
       <c r="F45" t="n">
-        <v>234</v>
+        <v>950</v>
       </c>
       <c r="G45" t="n">
-        <v>99684000</v>
+        <v>99940000</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1898,12 +1896,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1912,13 +1910,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105200</v>
+        <v>2370</v>
       </c>
       <c r="F46" t="n">
-        <v>950</v>
+        <v>421940</v>
       </c>
       <c r="G46" t="n">
-        <v>99940000</v>
+        <v>999997800</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1930,12 +1928,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1944,13 +1942,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2370</v>
+        <v>54200</v>
       </c>
       <c r="F47" t="n">
-        <v>421940</v>
+        <v>2767</v>
       </c>
       <c r="G47" t="n">
-        <v>999997800</v>
+        <v>149971400</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1962,12 +1960,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1976,47 +1974,15 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>54200</v>
+        <v>8320</v>
       </c>
       <c r="F48" t="n">
-        <v>2767</v>
+        <v>6009</v>
       </c>
       <c r="G48" t="n">
-        <v>149971400</v>
+        <v>49994880</v>
       </c>
       <c r="H48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>파인엠텍</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>441270</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>8320</v>
-      </c>
-      <c r="F49" t="n">
-        <v>6009</v>
-      </c>
-      <c r="G49" t="n">
-        <v>49994880</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,31 +478,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>와이지-원</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>019210</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13620</v>
+        <v>25800</v>
       </c>
       <c r="F2" t="n">
-        <v>3604</v>
+        <v>2713</v>
       </c>
       <c r="G2" t="n">
-        <v>49086480</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-4.49</v>
-      </c>
+        <v>69995400</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,12 +510,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25050</v>
+        <v>206500</v>
       </c>
       <c r="F3" t="n">
-        <v>3887</v>
+        <v>338</v>
       </c>
       <c r="G3" t="n">
-        <v>97369350</v>
+        <v>69797000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -544,12 +542,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,13 +556,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>194600</v>
+        <v>70100</v>
       </c>
       <c r="F4" t="n">
-        <v>250</v>
+        <v>998</v>
       </c>
       <c r="G4" t="n">
-        <v>48650000</v>
+        <v>69959800</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -576,27 +574,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21200</v>
+        <v>93300</v>
       </c>
       <c r="F5" t="n">
-        <v>322</v>
+        <v>214</v>
       </c>
       <c r="G5" t="n">
-        <v>6826400</v>
+        <v>19966200</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -608,27 +606,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>68900</v>
+        <v>11300</v>
       </c>
       <c r="F6" t="n">
-        <v>271</v>
+        <v>4424</v>
       </c>
       <c r="G6" t="n">
-        <v>18671900</v>
+        <v>49991200</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,12 +638,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,13 +652,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>91300</v>
+        <v>19740</v>
       </c>
       <c r="F7" t="n">
-        <v>213</v>
+        <v>2532</v>
       </c>
       <c r="G7" t="n">
-        <v>19446900</v>
+        <v>49981680</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -672,27 +670,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19930</v>
+        <v>25150</v>
       </c>
       <c r="F8" t="n">
-        <v>7563</v>
+        <v>2385</v>
       </c>
       <c r="G8" t="n">
-        <v>150730590</v>
+        <v>59982750</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -704,27 +702,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22500</v>
+        <v>22050</v>
       </c>
       <c r="F9" t="n">
-        <v>2034</v>
+        <v>2267</v>
       </c>
       <c r="G9" t="n">
-        <v>45765000</v>
+        <v>49987350</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,27 +734,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20550</v>
+        <v>43150</v>
       </c>
       <c r="F10" t="n">
-        <v>119</v>
+        <v>1390</v>
       </c>
       <c r="G10" t="n">
-        <v>2445450</v>
+        <v>59978500</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,12 +766,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>케이아이엔엑스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093320</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,13 +780,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>139000</v>
+        <v>310000</v>
       </c>
       <c r="F11" t="n">
-        <v>420</v>
+        <v>225</v>
       </c>
       <c r="G11" t="n">
-        <v>58380000</v>
+        <v>69750000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,27 +798,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31450</v>
+        <v>6240</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>3205</v>
       </c>
       <c r="G12" t="n">
-        <v>1981350</v>
+        <v>19999200</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,12 +830,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,13 +844,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>41300</v>
+        <v>24000</v>
       </c>
       <c r="F13" t="n">
-        <v>1179</v>
+        <v>833</v>
       </c>
       <c r="G13" t="n">
-        <v>48692700</v>
+        <v>19992000</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,12 +862,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,13 +876,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>284000</v>
+        <v>90300</v>
       </c>
       <c r="F14" t="n">
-        <v>240</v>
+        <v>442</v>
       </c>
       <c r="G14" t="n">
-        <v>68160000</v>
+        <v>39912600</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -896,12 +894,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -910,13 +908,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21100</v>
+        <v>279500</v>
       </c>
       <c r="F15" t="n">
-        <v>923</v>
+        <v>357</v>
       </c>
       <c r="G15" t="n">
-        <v>19475300</v>
+        <v>99781500</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -928,27 +926,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>277000</v>
+        <v>366000</v>
       </c>
       <c r="F16" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>28531000</v>
+        <v>19764000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,12 +958,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -974,13 +972,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>369000</v>
+        <v>91000</v>
       </c>
       <c r="F17" t="n">
-        <v>132</v>
+        <v>659</v>
       </c>
       <c r="G17" t="n">
-        <v>48708000</v>
+        <v>59969000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -992,27 +990,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>91900</v>
+        <v>120100</v>
       </c>
       <c r="F18" t="n">
-        <v>485</v>
+        <v>666</v>
       </c>
       <c r="G18" t="n">
-        <v>44571500</v>
+        <v>79986600</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1024,27 +1022,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115800</v>
+        <v>2405</v>
       </c>
       <c r="F19" t="n">
-        <v>391</v>
+        <v>415800</v>
       </c>
       <c r="G19" t="n">
-        <v>45277800</v>
+        <v>999999000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1056,27 +1054,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>46250</v>
+        <v>69000</v>
       </c>
       <c r="F20" t="n">
-        <v>1720</v>
+        <v>579</v>
       </c>
       <c r="G20" t="n">
-        <v>79550000</v>
+        <v>39951000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1102,13 +1100,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>34500</v>
+        <v>42300</v>
       </c>
       <c r="F21" t="n">
-        <v>847</v>
+        <v>709</v>
       </c>
       <c r="G21" t="n">
-        <v>29221500</v>
+        <v>29990700</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1120,869 +1118,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8070</v>
+        <v>23350</v>
       </c>
       <c r="F22" t="n">
-        <v>5496</v>
+        <v>856</v>
       </c>
       <c r="G22" t="n">
-        <v>44352720</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>와이지-원</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>019210</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>14260</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3604</v>
-      </c>
-      <c r="G23" t="n">
-        <v>51393040</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>동성화인텍</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>033500</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>편출</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>17160</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5549</v>
-      </c>
-      <c r="G24" t="n">
-        <v>95220840</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-4.77</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>한스바이오메드</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>042520</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>19630</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2618</v>
-      </c>
-      <c r="G25" t="n">
-        <v>51391340</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>리노공업</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>058470</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>66600</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1543</v>
-      </c>
-      <c r="G26" t="n">
-        <v>102763800</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>유니테스트</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>086390</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>편출</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>11330</v>
-      </c>
-      <c r="F27" t="n">
-        <v>9157</v>
-      </c>
-      <c r="G27" t="n">
-        <v>103748810</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>086450</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>비중 확대</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>21600</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2776</v>
-      </c>
-      <c r="G28" t="n">
-        <v>59961600</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>089890</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>비중 확대</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>22200</v>
-      </c>
-      <c r="F29" t="n">
-        <v>366</v>
-      </c>
-      <c r="G29" t="n">
-        <v>8125200</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>091580</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>20650</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2488</v>
-      </c>
-      <c r="G30" t="n">
-        <v>51377200</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>씨젠</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>096530</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>비중 확대</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>31900</v>
-      </c>
-      <c r="F31" t="n">
-        <v>123</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3923700</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>196170</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>비중 축소</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>288500</v>
-      </c>
-      <c r="F32" t="n">
-        <v>147</v>
-      </c>
-      <c r="G32" t="n">
-        <v>42409500</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>파마리서치</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>214450</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>편출</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>386500</v>
-      </c>
-      <c r="F33" t="n">
-        <v>234</v>
-      </c>
-      <c r="G33" t="n">
-        <v>90441000</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-9.27</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>에스티팜</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>237690</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>비중 확대</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>101200</v>
-      </c>
-      <c r="F34" t="n">
-        <v>65</v>
-      </c>
-      <c r="G34" t="n">
-        <v>6578000</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>240810</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>114800</v>
-      </c>
-      <c r="F35" t="n">
-        <v>895</v>
-      </c>
-      <c r="G35" t="n">
-        <v>102746000</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>257720</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>비중 축소</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>48000</v>
-      </c>
-      <c r="F36" t="n">
-        <v>626</v>
-      </c>
-      <c r="G36" t="n">
-        <v>30048000</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>파인엠텍</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>441270</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>비중 축소</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>9350</v>
-      </c>
-      <c r="F37" t="n">
-        <v>513</v>
-      </c>
-      <c r="G37" t="n">
-        <v>4796550</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>동성화인텍</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>033500</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>18020</v>
-      </c>
-      <c r="F38" t="n">
-        <v>5549</v>
-      </c>
-      <c r="G38" t="n">
-        <v>99992980</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>유니테스트</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>086390</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>10920</v>
-      </c>
-      <c r="F39" t="n">
-        <v>9157</v>
-      </c>
-      <c r="G39" t="n">
-        <v>99994440</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>086450</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>22250</v>
-      </c>
-      <c r="F40" t="n">
-        <v>6741</v>
-      </c>
-      <c r="G40" t="n">
-        <v>149987250</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>089890</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>23450</v>
-      </c>
-      <c r="F41" t="n">
-        <v>4264</v>
-      </c>
-      <c r="G41" t="n">
-        <v>99990800</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>씨젠</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>096530</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>33600</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1488</v>
-      </c>
-      <c r="G42" t="n">
-        <v>49996800</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>196170</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>307500</v>
-      </c>
-      <c r="F43" t="n">
-        <v>325</v>
-      </c>
-      <c r="G43" t="n">
-        <v>99937500</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>파마리서치</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>214450</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>426000</v>
-      </c>
-      <c r="F44" t="n">
-        <v>234</v>
-      </c>
-      <c r="G44" t="n">
-        <v>99684000</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>에스티팜</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>237690</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>105200</v>
-      </c>
-      <c r="F45" t="n">
-        <v>950</v>
-      </c>
-      <c r="G45" t="n">
-        <v>99940000</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>KODEX 코스닥150선물인버스</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>251340</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>2370</v>
-      </c>
-      <c r="F46" t="n">
-        <v>421940</v>
-      </c>
-      <c r="G46" t="n">
-        <v>999997800</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>257720</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>54200</v>
-      </c>
-      <c r="F47" t="n">
-        <v>2767</v>
-      </c>
-      <c r="G47" t="n">
-        <v>149971400</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>파인엠텍</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>441270</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>8320</v>
-      </c>
-      <c r="F48" t="n">
-        <v>6009</v>
-      </c>
-      <c r="G48" t="n">
-        <v>49994880</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>19987600</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
